--- a/Full-LC-AUTO/data inputs/trouser/Additional-Description-inputs.xlsx
+++ b/Full-LC-AUTO/data inputs/trouser/Additional-Description-inputs.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C4C500-9494-4473-9B37-B140F8671832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Trouser Addl Desc Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Trouser Field Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -236,9 +230,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>black jogger for men, black joggers men, black joggers for men, black track pant, black track pants for men, black trouser for men, black trousers men, black cargo joggers, black cotton joggers, black relaxed fit joggers, black loose fit joggers, black gym joggers, black sports joggers, black casual trousers, black ankle fit joggers, black stretchable joggers, black lounge pants, black lower for men, black pajama for men, black bottom wear men, kaala jogger, kaala lower, kaala track pant, kaala pajama, kaale trouser, kaale pant, kaala bottom wear,trouser for men, trousers men, formal trouser men, casual trouser for men, cotton trouser men, relaxed fit trousers, loose fit trousers, stretchable trousers, smart casual trousers, everyday trousers, office wear trousers, comfortable trousers for men, ankle fit trousers, straight fit trousers, designer trousers for men, cotton pants for men, pant for men, mens pants, mardana trouser, mardon ke trouser, aaramdayak pant, cotton pant,night suit for men, men night suit, mens night suit, cotton night suit for men, soft night suit for men, comfortable night suit, premium night suit men, night dress for men, men sleepwear, mens sleepwear, sleep suit for men, lounge wear set for men, home wear set for men, night wear for men, mens night wear, cotton sleepwear men, full sleeve night suit, half sleeve night suit, comfortable sleep suit, soft cotton sleep suit, raat ka suit, night dress mardana, sone wala kapda, raat ka kapda,pajama</t>
-  </si>
-  <si>
     <t>Upgrade your everyday wardrobe with these Men's Black Relaxed Fit Trousers, designed for maximum comfort and effortless style. Crafted from soft, breathable fabric, these trousers provide a smooth feel against the skin while ensuring all-day comfort. The relaxed fit offers ease of movement, making them perfect for casual outings, travel, lounging, work-from-home, or daily wear.</t>
   </si>
   <si>
@@ -267,13 +258,16 @@
   </si>
   <si>
     <t>Do not bleach,Easy Wash</t>
+  </si>
+  <si>
+    <t>black joggers for men, black jogger for men, black track pants for men, black trouser for men, black trousers men, black cotton joggers, black relaxed fit joggers, black loose fit joggers, black gym joggers, black sports joggers, black casual trousers, black stretchable joggers, black lounge pants, black lower for men, black pajama for men, kaala jogger, kaala lower, kaala track pant, kaala pajama, kaale trouser, trouser for men, casual trouser for men, cotton trouser men, relaxed fit trousers, loose fit trousers, stretchable trousers, comfortable trousers for men, straight fit trousers, cotton pants for men, mens pants, mardana trouser, aaramdayak pant, cotton pant, night suit for men, mens night suit, cotton night suit for men, soft night suit for men, men sleepwear, sleep suit for men, lounge wear set for men, home wear set for men, night wear for men, cotton sleepwear men, comfortable sleep suit, soft cotton sleep suit, raat ka suit, night dress mardana, pajama.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,9 +605,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="7" width="18" customWidth="1"/>
@@ -624,7 +618,7 @@
     <col min="28" max="28" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -710,7 +704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -736,55 +730,55 @@
         <v>70</v>
       </c>
       <c r="J2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" t="s">
         <v>72</v>
       </c>
-      <c r="K2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="s">
         <v>73</v>
-      </c>
-      <c r="O2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>74</v>
       </c>
       <c r="R2" t="s">
         <v>69</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U2" t="s">
         <v>69</v>
       </c>
       <c r="V2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W2">
         <v>35</v>
       </c>
       <c r="X2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" t="s">
-        <v>79</v>
-      </c>
       <c r="AA2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -810,55 +804,55 @@
         <v>70</v>
       </c>
       <c r="J3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" t="s">
         <v>72</v>
       </c>
-      <c r="K3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="s">
         <v>73</v>
-      </c>
-      <c r="O3" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>74</v>
       </c>
       <c r="R3" t="s">
         <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U3" t="s">
         <v>69</v>
       </c>
       <c r="V3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W3">
         <v>35</v>
       </c>
       <c r="X3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y3" t="s">
         <v>77</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>78</v>
       </c>
-      <c r="Z3" t="s">
-        <v>79</v>
-      </c>
       <c r="AA3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -884,52 +878,52 @@
         <v>70</v>
       </c>
       <c r="J4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4" t="s">
         <v>72</v>
       </c>
-      <c r="K4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q4" t="s">
         <v>73</v>
-      </c>
-      <c r="O4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>74</v>
       </c>
       <c r="R4" t="s">
         <v>69</v>
       </c>
       <c r="S4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U4" t="s">
         <v>69</v>
       </c>
       <c r="V4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W4">
         <v>35</v>
       </c>
       <c r="X4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y4" t="s">
         <v>77</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>78</v>
       </c>
-      <c r="Z4" t="s">
-        <v>79</v>
-      </c>
       <c r="AA4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -938,9 +932,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -948,7 +942,7 @@
     <col min="4" max="4" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -962,7 +956,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -976,7 +970,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -990,7 +984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1004,7 +998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1018,7 +1012,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1032,7 +1026,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1046,7 +1040,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1060,7 +1054,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1074,7 +1068,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1088,7 +1082,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1102,7 +1096,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1116,7 +1110,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1130,7 +1124,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1144,7 +1138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1158,7 +1152,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1172,7 +1166,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1186,7 +1180,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1200,7 +1194,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1214,7 +1208,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1228,7 +1222,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1242,7 +1236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1256,7 +1250,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1270,7 +1264,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1284,7 +1278,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1298,7 +1292,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1312,7 +1306,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>26</v>
       </c>
